--- a/Martinez_Ex3A_tables.xlsx
+++ b/Martinez_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alondramartinez\Documents\DataAnalytics\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E07170-C808-41EB-A340-0D537A25CD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6137466E-691A-4CD0-B16C-4FA73635EC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="570" windowWidth="28800" windowHeight="15285" activeTab="2" xr2:uid="{9E404D5B-5B67-4BBA-ABD8-8EFDC22DF197}"/>
+    <workbookView xWindow="60" yWindow="15" windowWidth="23010" windowHeight="13650" activeTab="3" xr2:uid="{9E404D5B-5B67-4BBA-ABD8-8EFDC22DF197}"/>
   </bookViews>
   <sheets>
     <sheet name="Client" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>CLIENT</t>
   </si>
@@ -63,9 +63,6 @@
     <t>ADDRESS</t>
   </si>
   <si>
-    <t>PREFERRED CONTACT METHOD</t>
-  </si>
-  <si>
     <t>DOG</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>Walking Specifics</t>
   </si>
   <si>
-    <t>Pet_ID</t>
-  </si>
-  <si>
     <t>Energy_level</t>
   </si>
   <si>
@@ -145,16 +139,123 @@
   </si>
   <si>
     <t>Walking_notes</t>
+  </si>
+  <si>
+    <t>PREFERRED_CONTACT_ METHOD</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>123-121-1123</t>
+  </si>
+  <si>
+    <t>jodoe@hotmail.com</t>
+  </si>
+  <si>
+    <t>1222 Random St Charlotte Nc 29872</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t>45 min</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Sam Smith</t>
+  </si>
+  <si>
+    <t>678-876-9908</t>
+  </si>
+  <si>
+    <t>2026-18-04</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>DOG_ID</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Labrador</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>122-222-3445</t>
+  </si>
+  <si>
+    <t>marj@hotmail.com</t>
+  </si>
+  <si>
+    <t>1344 seacrest st charlotte NC 29871</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>223-424-3399</t>
+  </si>
+  <si>
+    <t>juanl@hotmail.com</t>
+  </si>
+  <si>
+    <t>3333 east st Charlotte nc 25705</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -189,18 +290,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -533,12 +639,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B6FA3A-C159-4573-BA6F-C0F2CEA517FB}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" customWidth="1"/>
     <col min="7" max="7" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -567,57 +675,160 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{A04646B4-096F-42E5-BBD2-AB5F717D840C}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{FAF2187B-23E5-4247-B6A4-CCFFB938C591}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{23819D26-3730-4EC5-A6E6-C175455258A4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C529DC5D-C1CA-4049-9DF9-512152CFF537}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -627,39 +838,64 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97005BBC-6A80-46BB-A219-B56879358B98}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>123</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -679,21 +915,35 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>27</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -706,7 +956,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7656BA-CEA2-45CB-B15C-40FBD848A46A}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -719,30 +969,47 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
